--- a/database.xlsx
+++ b/database.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="355">
   <si>
     <t>NIVEL</t>
   </si>
@@ -307,6 +307,810 @@
   </si>
   <si>
     <t>Create a menu order.</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>On the Move</t>
+  </si>
+  <si>
+    <t>Connect with travel routines.</t>
+  </si>
+  <si>
+    <t>Present continuous (for actions now); Prepositions of movement; Imperatives</t>
+  </si>
+  <si>
+    <t>Talk about transportation; Describe travel routines; Give basic travel info</t>
+  </si>
+  <si>
+    <t>Present transport vocabulary.</t>
+  </si>
+  <si>
+    <t>Practice continuous forms.</t>
+  </si>
+  <si>
+    <t>Identify movement in listening.</t>
+  </si>
+  <si>
+    <t>Describe commuting routine.</t>
+  </si>
+  <si>
+    <t>Activate travel expressions.</t>
+  </si>
+  <si>
+    <t>Ask about transportation.</t>
+  </si>
+  <si>
+    <t>Practice imperatives.</t>
+  </si>
+  <si>
+    <t>Interpret travel signs.</t>
+  </si>
+  <si>
+    <t>Create travel plan.</t>
+  </si>
+  <si>
+    <t>What I Do Matters</t>
+  </si>
+  <si>
+    <t>Connect with job roles.</t>
+  </si>
+  <si>
+    <t>Can/Can't; Simple present; Job-related vocabulary</t>
+  </si>
+  <si>
+    <t>Talk about jobs; Responsibilities; Abilities; Workplace</t>
+  </si>
+  <si>
+    <t>Present job vocabulary.</t>
+  </si>
+  <si>
+    <t>Practice can/can't.</t>
+  </si>
+  <si>
+    <t>Identify job responsibilities.</t>
+  </si>
+  <si>
+    <t>Describe own skills.</t>
+  </si>
+  <si>
+    <t>Activate workplace expressions.</t>
+  </si>
+  <si>
+    <t>Ask about abilities.</t>
+  </si>
+  <si>
+    <t>Practice job verbs.</t>
+  </si>
+  <si>
+    <t>Interpret job ads.</t>
+  </si>
+  <si>
+    <t>Create job profile.</t>
+  </si>
+  <si>
+    <t>Feeling Good</t>
+  </si>
+  <si>
+    <t>Connect with emotions.</t>
+  </si>
+  <si>
+    <t>Be + adjectives; Should/Shouldn't; Health vocabulary</t>
+  </si>
+  <si>
+    <t>Express feelings; Talk about health; Give simple advice</t>
+  </si>
+  <si>
+    <t>Present feelings vocabulary.</t>
+  </si>
+  <si>
+    <t>Identify symptoms.</t>
+  </si>
+  <si>
+    <t>Describe current feelings.</t>
+  </si>
+  <si>
+    <t>Activate health expressions.</t>
+  </si>
+  <si>
+    <t>Ask for advice.</t>
+  </si>
+  <si>
+    <t>Practice should/shouldn't.</t>
+  </si>
+  <si>
+    <t>Interpret health posters.</t>
+  </si>
+  <si>
+    <t>Create health tips.</t>
+  </si>
+  <si>
+    <t>Let's Celebrate Life</t>
+  </si>
+  <si>
+    <t>Connect with celebrations.</t>
+  </si>
+  <si>
+    <t>Going to; Sequencing; Time expressions</t>
+  </si>
+  <si>
+    <t>Talk about holidays; Traditions; Invitations; Social plans</t>
+  </si>
+  <si>
+    <t>Present holiday vocabulary.</t>
+  </si>
+  <si>
+    <t>Practice going to.</t>
+  </si>
+  <si>
+    <t>Identify event details.</t>
+  </si>
+  <si>
+    <t>Describe personal traditions.</t>
+  </si>
+  <si>
+    <t>Activate social expressions.</t>
+  </si>
+  <si>
+    <t>Ask about plans.</t>
+  </si>
+  <si>
+    <t>Practice sequencing.</t>
+  </si>
+  <si>
+    <t>Interpret invitations.</t>
+  </si>
+  <si>
+    <t>Create celebration plan.</t>
+  </si>
+  <si>
+    <t>Plugged In</t>
+  </si>
+  <si>
+    <t>Connect with tech use.</t>
+  </si>
+  <si>
+    <t>Comparatives; Present simple; Tech verbs</t>
+  </si>
+  <si>
+    <t>Talk about technology; Describe devices; Express preferences</t>
+  </si>
+  <si>
+    <t>Present tech vocabulary.</t>
+  </si>
+  <si>
+    <t>Identify device functions.</t>
+  </si>
+  <si>
+    <t>Describe own devices.</t>
+  </si>
+  <si>
+    <t>Activate preference expressions.</t>
+  </si>
+  <si>
+    <t>Ask about devices.</t>
+  </si>
+  <si>
+    <t>Practice device verbs.</t>
+  </si>
+  <si>
+    <t>Interpret simple tech ads.</t>
+  </si>
+  <si>
+    <t>Create device comparison.</t>
+  </si>
+  <si>
+    <t>My Future, My Way</t>
+  </si>
+  <si>
+    <t>Connect with personal goals.</t>
+  </si>
+  <si>
+    <t>Going to; Want to; Infinitives for purpose</t>
+  </si>
+  <si>
+    <t>Express future dreams; Talk about goals; Describe aspirations</t>
+  </si>
+  <si>
+    <t>Present vocabulary for aspirations.</t>
+  </si>
+  <si>
+    <t>Practice going to + goals.</t>
+  </si>
+  <si>
+    <t>Identify future plans.</t>
+  </si>
+  <si>
+    <t>Present personal goals.</t>
+  </si>
+  <si>
+    <t>Activate purpose expressions.</t>
+  </si>
+  <si>
+    <t>Ask about aspirations.</t>
+  </si>
+  <si>
+    <t>Practice want to + verb.</t>
+  </si>
+  <si>
+    <t>Interpret future plans texts.</t>
+  </si>
+  <si>
+    <t>Create future vision statement.</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>Milestones that made me</t>
+  </si>
+  <si>
+    <t>Spot the milestone moments.</t>
+  </si>
+  <si>
+    <t>Past simple vs present perfect; Past perfect</t>
+  </si>
+  <si>
+    <t>Talking about present and past actions; Recount personal experiences using Past Simple and Present Perfect</t>
+  </si>
+  <si>
+    <t>Tell the story behind your milestone.</t>
+  </si>
+  <si>
+    <t>Words that shape your story / Grammar that helps you tell the story.</t>
+  </si>
+  <si>
+    <t>11–12</t>
+  </si>
+  <si>
+    <t>Put it into action.</t>
+  </si>
+  <si>
+    <t>Share your milestone story with the world.</t>
+  </si>
+  <si>
+    <t>Seeing the "before" behind your milestone.</t>
+  </si>
+  <si>
+    <t>Reveal the story behind your milestone.</t>
+  </si>
+  <si>
+    <t>Emotions before the moment / Grammar that shows what came first.</t>
+  </si>
+  <si>
+    <t>21–22</t>
+  </si>
+  <si>
+    <t>Understanding the before in real stories.</t>
+  </si>
+  <si>
+    <t>23–25</t>
+  </si>
+  <si>
+    <t>Share the story behind your milestone.</t>
+  </si>
+  <si>
+    <t>Work and Beyond</t>
+  </si>
+  <si>
+    <t>Step into the job world.</t>
+  </si>
+  <si>
+    <t>Comparatives and modal verbs to talk about jobs</t>
+  </si>
+  <si>
+    <t>Describe jobs, compare working conditions and discuss career preferences; Describe job duties and compare roles using modals and comparatives</t>
+  </si>
+  <si>
+    <t>Map the real world of work.</t>
+  </si>
+  <si>
+    <t>30–31</t>
+  </si>
+  <si>
+    <t>Words that make work clear / Grammar that describes and compares.</t>
+  </si>
+  <si>
+    <t>32–35</t>
+  </si>
+  <si>
+    <t>36–38</t>
+  </si>
+  <si>
+    <t>Now it's time to complete your mission!</t>
+  </si>
+  <si>
+    <t>39–40</t>
+  </si>
+  <si>
+    <t>What I really want in a job.</t>
+  </si>
+  <si>
+    <t>Recommend the right job match!</t>
+  </si>
+  <si>
+    <t>Words for choosing the job that fits you / Grammar that guides your choices.</t>
+  </si>
+  <si>
+    <t>44–45</t>
+  </si>
+  <si>
+    <t>Real voices, real choices!</t>
+  </si>
+  <si>
+    <t>46–48</t>
+  </si>
+  <si>
+    <t>Journeys &amp; Cultures</t>
+  </si>
+  <si>
+    <t>Journeys that shape us.</t>
+  </si>
+  <si>
+    <t>Ways to express preferences; Past simple vs past continuous</t>
+  </si>
+  <si>
+    <t>Share travel experiences, compare cultures and make recommendations; Share travel experiences using descriptive language</t>
+  </si>
+  <si>
+    <t>Share the journey.</t>
+  </si>
+  <si>
+    <t>Telling the story behind the trip / When moments unfold.</t>
+  </si>
+  <si>
+    <t>54–55</t>
+  </si>
+  <si>
+    <t>Journeys &amp; cultures.</t>
+  </si>
+  <si>
+    <t>56–58</t>
+  </si>
+  <si>
+    <t>59–60</t>
+  </si>
+  <si>
+    <t>What I notice, what I prefer.</t>
+  </si>
+  <si>
+    <t>Share your journey.</t>
+  </si>
+  <si>
+    <t>Preferences meet collaboration / Grammar for preferences and observation.</t>
+  </si>
+  <si>
+    <t>64–65</t>
+  </si>
+  <si>
+    <t>Different voices, different choices.</t>
+  </si>
+  <si>
+    <t>66–68</t>
+  </si>
+  <si>
+    <t>Screen Time &amp; Stories</t>
+  </si>
+  <si>
+    <t>Life on screen.</t>
+  </si>
+  <si>
+    <t>Modals for evaluation</t>
+  </si>
+  <si>
+    <t>Evaluate media and entertainment; Recommend content; Analyze its influence on daily life; Express preferences about movies, music and shows</t>
+  </si>
+  <si>
+    <t>Choose, compare and speak up.</t>
+  </si>
+  <si>
+    <t>Talking about what we enjoy / How opinions work.</t>
+  </si>
+  <si>
+    <t>74–75</t>
+  </si>
+  <si>
+    <t>Screens in real life: What people really choose.</t>
+  </si>
+  <si>
+    <t>76–78</t>
+  </si>
+  <si>
+    <t>What are you watching around the world?</t>
+  </si>
+  <si>
+    <t>Under the influence.</t>
+  </si>
+  <si>
+    <t>Your voice online.</t>
+  </si>
+  <si>
+    <t>Words, functions &amp; sound / Grammar that persuades.</t>
+  </si>
+  <si>
+    <t>83–84</t>
+  </si>
+  <si>
+    <t>85–87</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>Embrace Stress!</t>
+  </si>
+  <si>
+    <t>Gerunds and infinitives</t>
+  </si>
+  <si>
+    <t>Talking about jobs and stress</t>
+  </si>
+  <si>
+    <t>Dealing with stress.</t>
+  </si>
+  <si>
+    <t>High- and low-stress jobs.</t>
+  </si>
+  <si>
+    <t>The stressed-out generation.</t>
+  </si>
+  <si>
+    <t>18–19</t>
+  </si>
+  <si>
+    <t>How to make stress your friend.</t>
+  </si>
+  <si>
+    <t>Managing stress.</t>
+  </si>
+  <si>
+    <t>Media Influences</t>
+  </si>
+  <si>
+    <t>Media Influences.</t>
+  </si>
+  <si>
+    <t>Relative clauses</t>
+  </si>
+  <si>
+    <t>Talking about media and inspirations</t>
+  </si>
+  <si>
+    <t>At the movies.</t>
+  </si>
+  <si>
+    <t>Media and the mind.</t>
+  </si>
+  <si>
+    <t>Are superheroes good role models?</t>
+  </si>
+  <si>
+    <t>How movies teach manhood.</t>
+  </si>
+  <si>
+    <t>33–34</t>
+  </si>
+  <si>
+    <t>Analyzing movies.</t>
+  </si>
+  <si>
+    <t>Development</t>
+  </si>
+  <si>
+    <t>Development.</t>
+  </si>
+  <si>
+    <t>Present perfect and present perfect progressive</t>
+  </si>
+  <si>
+    <t>Talking about change</t>
+  </si>
+  <si>
+    <t>Aspirations.</t>
+  </si>
+  <si>
+    <t>The next economic giant.</t>
+  </si>
+  <si>
+    <t>The economics of happiness.</t>
+  </si>
+  <si>
+    <t>42–43</t>
+  </si>
+  <si>
+    <t>Global population growth, box by box.</t>
+  </si>
+  <si>
+    <t>45–46</t>
+  </si>
+  <si>
+    <t>Rich and poor.</t>
+  </si>
+  <si>
+    <t>48–50</t>
+  </si>
+  <si>
+    <t>Secrets and Lies</t>
+  </si>
+  <si>
+    <t>Secrets and Lies.</t>
+  </si>
+  <si>
+    <t>Modals of deduction and speculation</t>
+  </si>
+  <si>
+    <t>Speculating about the truth</t>
+  </si>
+  <si>
+    <t>Truth and lies.</t>
+  </si>
+  <si>
+    <t>Truth and pictures.</t>
+  </si>
+  <si>
+    <t>Lies we need to tell.</t>
+  </si>
+  <si>
+    <t>56–57</t>
+  </si>
+  <si>
+    <t>How to spot a liar.</t>
+  </si>
+  <si>
+    <t>Liespotting.</t>
+  </si>
+  <si>
+    <t>To the Edge</t>
+  </si>
+  <si>
+    <t>To the Edge.</t>
+  </si>
+  <si>
+    <t>Past perfect and past perfect progressive</t>
+  </si>
+  <si>
+    <t>Describing accomplishments</t>
+  </si>
+  <si>
+    <t>Challenge and success.</t>
+  </si>
+  <si>
+    <t>Superhumans.</t>
+  </si>
+  <si>
+    <t>66–67</t>
+  </si>
+  <si>
+    <t>Magic Man.</t>
+  </si>
+  <si>
+    <t>68–69</t>
+  </si>
+  <si>
+    <t>How I held my breath for 17 minutes.</t>
+  </si>
+  <si>
+    <t>Explaining achievements.</t>
+  </si>
+  <si>
+    <t>Money Matters</t>
+  </si>
+  <si>
+    <t>Money Matters.</t>
+  </si>
+  <si>
+    <t>Phrasal verbs</t>
+  </si>
+  <si>
+    <t>Using phrasal verbs</t>
+  </si>
+  <si>
+    <t>Money.</t>
+  </si>
+  <si>
+    <t>What we're saving for.</t>
+  </si>
+  <si>
+    <t>Giving something back.</t>
+  </si>
+  <si>
+    <t>80–81</t>
+  </si>
+  <si>
+    <t>Why giving away our wealth has been the most satisfying thing we've done.</t>
+  </si>
+  <si>
+    <t>Creating a charity.</t>
+  </si>
+  <si>
+    <t>86–88</t>
+  </si>
+  <si>
+    <t>Medical Frontiers</t>
+  </si>
+  <si>
+    <t>Medical Frontiers.</t>
+  </si>
+  <si>
+    <t>Modals of probability</t>
+  </si>
+  <si>
+    <t>Making predictions</t>
+  </si>
+  <si>
+    <t>Innovation.</t>
+  </si>
+  <si>
+    <t>The future of medicine.</t>
+  </si>
+  <si>
+    <t>Just Press "Print".</t>
+  </si>
+  <si>
+    <t>94–95</t>
+  </si>
+  <si>
+    <t>The sore problem of prosthetics.</t>
+  </si>
+  <si>
+    <t>97–98</t>
+  </si>
+  <si>
+    <t>Inventing solutions.</t>
+  </si>
+  <si>
+    <t>Life Decisions</t>
+  </si>
+  <si>
+    <t>Life Decisions.</t>
+  </si>
+  <si>
+    <t>Future perfect and future perfect progressive</t>
+  </si>
+  <si>
+    <t>Talking about milestones</t>
+  </si>
+  <si>
+    <t>Entering adulthood.</t>
+  </si>
+  <si>
+    <t>Plans and aspirations.</t>
+  </si>
+  <si>
+    <t>The defining decade.</t>
+  </si>
+  <si>
+    <t>106–107</t>
+  </si>
+  <si>
+    <t>Why 30 is not the new 20.</t>
+  </si>
+  <si>
+    <t>Hard choices.</t>
+  </si>
+  <si>
+    <t>Technology and Innovation</t>
+  </si>
+  <si>
+    <t>Technology and Innovation.</t>
+  </si>
+  <si>
+    <t>First and second conditional</t>
+  </si>
+  <si>
+    <t>Talking about conditions</t>
+  </si>
+  <si>
+    <t>Technologies that make a difference.</t>
+  </si>
+  <si>
+    <t>Driverless cars.</t>
+  </si>
+  <si>
+    <t>Drones are here to stay.</t>
+  </si>
+  <si>
+    <t>118–119</t>
+  </si>
+  <si>
+    <t>Robots that fly... and cooperate.</t>
+  </si>
+  <si>
+    <t>124–126</t>
+  </si>
+  <si>
+    <t>Connections</t>
+  </si>
+  <si>
+    <t>Connections.</t>
+  </si>
+  <si>
+    <t>Reported speech</t>
+  </si>
+  <si>
+    <t>Reporting what someone said</t>
+  </si>
+  <si>
+    <t>Our listening.</t>
+  </si>
+  <si>
+    <t>Sound facts.</t>
+  </si>
+  <si>
+    <t>The lost art of listening?</t>
+  </si>
+  <si>
+    <t>132–133</t>
+  </si>
+  <si>
+    <t>Five ways to listen better.</t>
+  </si>
+  <si>
+    <t>135–136</t>
+  </si>
+  <si>
+    <t>Conscious listening.</t>
+  </si>
+  <si>
+    <t>Life in the Slow Lane</t>
+  </si>
+  <si>
+    <t>Life in the Slow Lane.</t>
+  </si>
+  <si>
+    <t>Articles and quantifiers</t>
+  </si>
+  <si>
+    <t>Talking about quantity</t>
+  </si>
+  <si>
+    <t>The slow movement.</t>
+  </si>
+  <si>
+    <t>Time to monotask.</t>
+  </si>
+  <si>
+    <t>Your brain on nature.</t>
+  </si>
+  <si>
+    <t>Cloudy with a chance of joy.</t>
+  </si>
+  <si>
+    <t>Changing the pace.</t>
+  </si>
+  <si>
+    <t>Make Yourself Heard</t>
+  </si>
+  <si>
+    <t>Make Yourself Heard.</t>
+  </si>
+  <si>
+    <t>Third and mixed conditionals</t>
+  </si>
+  <si>
+    <t>Talking about the imaginary past</t>
+  </si>
+  <si>
+    <t>Expressing yourself.</t>
+  </si>
+  <si>
+    <t>Disasters.</t>
+  </si>
+  <si>
+    <t>Whistleblowers.</t>
+  </si>
+  <si>
+    <t>156–157</t>
+  </si>
+  <si>
+    <t>Dare to disagree.</t>
+  </si>
+  <si>
+    <t>What should we do?</t>
+  </si>
+  <si>
+    <t>162–164</t>
   </si>
 </sst>
 </file>
@@ -340,12 +1144,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2153,6 +2960,5726 @@
         <v>125.0</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B62" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62" s="1">
+        <v>127.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B63" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D63" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H63" s="1">
+        <v>128.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B64" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D64" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H64" s="1">
+        <v>129.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B65" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D65" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H65" s="1">
+        <v>132.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B66" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D66" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H66" s="1">
+        <v>134.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B67" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H67" s="1">
+        <v>137.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B68" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D68" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H68" s="1">
+        <v>138.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B69" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D69" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H69" s="1">
+        <v>139.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B70" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D70" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H70" s="1">
+        <v>141.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B71" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D71" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H71" s="1">
+        <v>145.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B72" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D72" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H72" s="1">
+        <v>147.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B73" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D73" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H73" s="1">
+        <v>148.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B74" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D74" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H74" s="1">
+        <v>149.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B75" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D75" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H75" s="1">
+        <v>152.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D76" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H76" s="1">
+        <v>154.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B77" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D77" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H77" s="1">
+        <v>157.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B78" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D78" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H78" s="1">
+        <v>158.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D79" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H79" s="1">
+        <v>159.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D80" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H80" s="1">
+        <v>161.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D81" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H81" s="1">
+        <v>164.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B82" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H82" s="1">
+        <v>166.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D83" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H83" s="1">
+        <v>167.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D84" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H84" s="1">
+        <v>168.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B85" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D85" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H85" s="1">
+        <v>170.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D86" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H86" s="1">
+        <v>172.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D87" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H87" s="1">
+        <v>174.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D88" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H88" s="1">
+        <v>175.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B89" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H89" s="1">
+        <v>176.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B90" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D90" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H90" s="1">
+        <v>178.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B91" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D91" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H91" s="1">
+        <v>180.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B92" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D92" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H92" s="1">
+        <v>202.0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B93" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D93" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H93" s="1">
+        <v>203.0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B94" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D94" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H94" s="1">
+        <v>204.0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B95" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D95" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H95" s="1">
+        <v>206.0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B96" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D96" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H96" s="1">
+        <v>209.0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B97" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D97" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H97" s="1">
+        <v>211.0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B98" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D98" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H98" s="1">
+        <v>212.0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B99" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D99" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H99" s="1">
+        <v>213.0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B100" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D100" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H100" s="1">
+        <v>217.0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B101" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D101" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H101" s="1">
+        <v>219.0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B102" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D102" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H102" s="1">
+        <v>183.0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B103" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D103" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H103" s="1">
+        <v>184.0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B104" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D104" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H104" s="1">
+        <v>185.0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B105" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D105" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H105" s="1">
+        <v>187.0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B106" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D106" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H106" s="1">
+        <v>190.0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B107" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D107" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H107" s="1">
+        <v>192.0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B108" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D108" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H108" s="1">
+        <v>193.0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B109" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D109" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H109" s="1">
+        <v>194.0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B110" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D110" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H110" s="1">
+        <v>196.0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B111" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D111" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H111" s="1">
+        <v>199.0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B112" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D112" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H112" s="1">
+        <v>222.0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B113" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D113" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H113" s="1">
+        <v>223.0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B114" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D114" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H114" s="1">
+        <v>224.0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B115" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D115" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H115" s="1">
+        <v>227.0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B116" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D116" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H116" s="1">
+        <v>230.0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B117" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D117" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H117" s="1">
+        <v>232.0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B118" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D118" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H118" s="1">
+        <v>233.0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B119" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D119" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H119" s="1">
+        <v>234.0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B120" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D120" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H120" s="1">
+        <v>236.0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B121" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D121" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H121" s="1">
+        <v>239.0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B122" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D122" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H122" s="1">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B123" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D123" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H123" s="1">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B124" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D124" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B125" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D125" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H125" s="1">
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B126" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D126" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H126" s="1">
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B127" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D127" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H127" s="1">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B128" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D128" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H128" s="1">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B129" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D129" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B130" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D130" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B131" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D131" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H131" s="1">
+        <v>26.0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B132" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D132" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H132" s="1">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B133" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D133" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B134" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D134" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B135" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D135" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B136" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D136" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B137" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D137" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H137" s="1">
+        <v>42.0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B138" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D138" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H138" s="1">
+        <v>43.0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B139" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D139" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B140" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D140" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B141" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D141" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H141" s="1">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B142" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D142" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H142" s="1">
+        <v>52.0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B143" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D143" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H143" s="1">
+        <v>53.0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B144" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D144" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B145" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D145" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B146" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D146" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B147" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D147" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H147" s="1">
+        <v>62.0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B148" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D148" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H148" s="1">
+        <v>63.0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B149" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D149" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B150" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D150" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B151" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D151" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H151" s="1">
+        <v>69.0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B152" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D152" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H152" s="1">
+        <v>72.0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B153" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D153" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H153" s="1">
+        <v>73.0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B154" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D154" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B155" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D155" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B156" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D156" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H156" s="1">
+        <v>79.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B157" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D157" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H157" s="1">
+        <v>81.0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B158" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D158" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H158" s="1">
+        <v>82.0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B159" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D159" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B160" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D160" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B161" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D161" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H161" s="1">
+        <v>88.0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B162" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D162" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H162" s="1">
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B163" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D163" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H163" s="1">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B164" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D164" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H164" s="1">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B165" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D165" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H165" s="1">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B166" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D166" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H166" s="1">
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B167" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D167" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B168" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D168" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H168" s="1">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B169" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D169" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H169" s="1">
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B170" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D170" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H170" s="1">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B171" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D171" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H171" s="1">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B172" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D172" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H172" s="1">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B173" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D173" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H173" s="1">
+        <v>26.0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B174" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D174" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H174" s="1">
+        <v>27.0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B175" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D175" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H175" s="1">
+        <v>27.0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B176" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D176" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H176" s="1">
+        <v>28.0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B177" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D177" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B178" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D178" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H178" s="1">
+        <v>32.0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B179" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D179" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B180" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D180" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H180" s="1">
+        <v>35.0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B181" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D181" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H181" s="1">
+        <v>36.0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B182" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D182" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H182" s="1">
+        <v>37.0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B183" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D183" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H183" s="1">
+        <v>38.0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B184" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D184" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H184" s="1">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B185" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D185" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H185" s="1">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B186" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D186" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H186" s="1">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B187" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D187" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B188" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D188" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H188" s="1">
+        <v>44.0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B189" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D189" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H189" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B190" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D190" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H190" s="1">
+        <v>47.0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B191" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D191" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B192" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D192" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H192" s="1">
+        <v>51.0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B193" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D193" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H193" s="1">
+        <v>52.0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B194" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D194" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H194" s="1">
+        <v>53.0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B195" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D195" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H195" s="1">
+        <v>53.0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B196" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D196" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H196" s="1">
+        <v>54.0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B197" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D197" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B198" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D198" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H198" s="1">
+        <v>58.0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B199" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D199" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H199" s="1">
+        <v>59.0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B200" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D200" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H200" s="1">
+        <v>61.0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B201" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D201" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H201" s="1">
+        <v>62.0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B202" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D202" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H202" s="1">
+        <v>63.0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B203" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D203" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H203" s="1">
+        <v>64.0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B204" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D204" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H204" s="1">
+        <v>65.0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B205" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D205" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H205" s="1">
+        <v>65.0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B206" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D206" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B207" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D207" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B208" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D208" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H208" s="1">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B209" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D209" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H209" s="1">
+        <v>71.0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B210" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D210" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H210" s="1">
+        <v>72.0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B211" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D211" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H211" s="1">
+        <v>74.0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B212" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D212" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H212" s="1">
+        <v>75.0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B213" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D213" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H213" s="1">
+        <v>76.0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B214" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D214" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H214" s="1">
+        <v>77.0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B215" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D215" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H215" s="1">
+        <v>77.0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B216" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D216" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H216" s="1">
+        <v>78.0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B217" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D217" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B218" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D218" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H218" s="1">
+        <v>82.0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B219" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D219" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H219" s="1">
+        <v>83.0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B220" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D220" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G220" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H220" s="1">
+        <v>85.0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B221" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D221" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G221" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H221" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B222" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D222" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G222" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H222" s="1">
+        <v>89.0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B223" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D223" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G223" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H223" s="1">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B224" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D224" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G224" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H224" s="1">
+        <v>91.0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B225" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D225" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G225" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H225" s="1">
+        <v>91.0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B226" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D226" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H226" s="1">
+        <v>92.0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B227" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D227" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H227" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B228" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D228" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G228" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H228" s="1">
+        <v>96.0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B229" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D229" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G229" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H229" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B230" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D230" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G230" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H230" s="1">
+        <v>99.0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B231" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D231" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G231" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H231" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B232" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D232" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G232" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H232" s="1">
+        <v>101.0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B233" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D233" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G233" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H233" s="1">
+        <v>102.0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B234" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D234" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G234" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H234" s="1">
+        <v>103.0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B235" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D235" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G235" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H235" s="1">
+        <v>103.0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B236" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D236" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G236" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H236" s="1">
+        <v>104.0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B237" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D237" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F237" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G237" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B238" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D238" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G238" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H238" s="1">
+        <v>108.0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B239" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D239" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G239" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H239" s="1">
+        <v>109.0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B240" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D240" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H240" s="1">
+        <v>111.0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B241" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D241" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G241" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H241" s="1">
+        <v>112.0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B242" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D242" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H242" s="1">
+        <v>113.0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B243" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D243" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G243" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H243" s="1">
+        <v>114.0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B244" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D244" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G244" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H244" s="1">
+        <v>115.0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B245" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D245" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F245" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G245" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H245" s="1">
+        <v>115.0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B246" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D246" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F246" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G246" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H246" s="1">
+        <v>116.0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B247" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D247" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="F247" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G247" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H247" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B248" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D248" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G248" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H248" s="1">
+        <v>120.0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B249" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D249" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F249" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G249" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H249" s="1">
+        <v>121.0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B250" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D250" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G250" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H250" s="1">
+        <v>123.0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B251" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D251" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G251" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H251" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B252" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D252" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G252" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H252" s="1">
+        <v>127.0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B253" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D253" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G253" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H253" s="1">
+        <v>128.0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B254" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D254" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G254" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H254" s="1">
+        <v>129.0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B255" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D255" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G255" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H255" s="1">
+        <v>129.0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B256" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D256" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F256" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G256" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H256" s="1">
+        <v>130.0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B257" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D257" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G257" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H257" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B258" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D258" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F258" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G258" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H258" s="1">
+        <v>134.0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B259" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D259" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G259" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H259" s="1">
+        <v>135.0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B260" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D260" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="F260" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G260" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H260" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B261" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D261" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F261" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G261" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H261" s="1">
+        <v>138.0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B262" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D262" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G262" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H262" s="1">
+        <v>139.0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B263" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D263" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F263" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G263" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H263" s="1">
+        <v>140.0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B264" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D264" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G264" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H264" s="1">
+        <v>141.0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B265" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D265" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G265" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H265" s="1">
+        <v>141.0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B266" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D266" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G266" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H266" s="1">
+        <v>142.0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B267" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D267" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F267" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G267" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H267" s="1">
+        <v>144.0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B268" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D268" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F268" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G268" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H268" s="1">
+        <v>144.0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B269" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D269" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="F269" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G269" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H269" s="1">
+        <v>147.0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B270" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D270" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G270" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H270" s="1">
+        <v>149.0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B271" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D271" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F271" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G271" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H271" s="1">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B272" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D272" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F272" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G272" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H272" s="1">
+        <v>151.0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B273" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D273" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F273" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G273" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H273" s="1">
+        <v>152.0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B274" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D274" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F274" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G274" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H274" s="1">
+        <v>153.0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B275" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D275" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F275" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G275" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H275" s="1">
+        <v>153.0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B276" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D276" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F276" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G276" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H276" s="1">
+        <v>154.0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B277" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D277" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F277" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G277" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H277" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B278" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D278" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F278" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G278" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H278" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B279" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D279" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F279" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G279" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H279" s="1">
+        <v>159.0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B280" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D280" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F280" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G280" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H280" s="1">
+        <v>159.0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B281" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D281" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F281" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G281" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H281" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
